--- a/Data/FlightPlan/FPL_06OCT26.xlsx
+++ b/Data/FlightPlan/FPL_06OCT26.xlsx
@@ -158,7 +158,7 @@
     <t>07:30</t>
   </si>
   <si>
-    <t>07:33</t>
+    <t>07:32</t>
   </si>
   <si>
     <t>08:00</t>
@@ -386,9 +386,6 @@
     <t>05:30</t>
   </si>
   <si>
-    <t>07:32</t>
-  </si>
-  <si>
     <t>08:40</t>
   </si>
   <si>
@@ -797,6 +794,9 @@
     <t>THD</t>
   </si>
   <si>
+    <t>09:06</t>
+  </si>
+  <si>
     <t>BKK</t>
   </si>
   <si>
@@ -824,24 +824,24 @@
     <t>06:42</t>
   </si>
   <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
     <t>HKT</t>
   </si>
   <si>
     <t>10:55</t>
   </si>
   <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -965,222 +965,234 @@
     <t>06:35</t>
   </si>
   <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>DYG</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>08:47</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>06:46</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>07:02</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>24 *</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>DYG</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:01</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>06:46</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>07:02</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:37</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>24 *</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
     <t>VN-A697</t>
   </si>
   <si>
+    <t>12:34</t>
+  </si>
+  <si>
     <t>13:25</t>
   </si>
   <si>
@@ -1211,9 +1223,6 @@
     <t>SVO</t>
   </si>
   <si>
-    <t>13:47</t>
-  </si>
-  <si>
     <t>05:15</t>
   </si>
   <si>
@@ -1241,7 +1250,7 @@
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 06, 2026 06:36</t>
+    <t xml:space="preserve">Generated on  Oct 06, 2026 07:13</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3337,7 +3346,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>125</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3364,10 +3373,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I59" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="J59" s="7">
         <v>126</v>
-      </c>
-      <c t="s" r="J59" s="7">
-        <v>127</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3397,10 +3406,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I60" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="J60" s="7">
         <v>128</v>
-      </c>
-      <c t="s" r="J60" s="7">
-        <v>129</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3463,10 +3472,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I62" s="7">
+        <v>129</v>
+      </c>
+      <c t="s" r="J62" s="7">
         <v>130</v>
-      </c>
-      <c t="s" r="J62" s="7">
-        <v>131</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3496,10 +3505,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I63" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="J63" s="7">
         <v>132</v>
-      </c>
-      <c t="s" r="J63" s="7">
-        <v>133</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3532,7 +3541,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3541,10 +3550,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>101</v>
@@ -3565,13 +3574,13 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
+        <v>133</v>
+      </c>
+      <c r="F66" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G66" s="8">
         <v>134</v>
-      </c>
-      <c r="F66" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G66" s="8">
-        <v>135</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>57</v>
@@ -3598,7 +3607,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3610,10 +3619,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3646,7 +3655,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3661,7 +3670,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3681,7 +3690,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3693,10 +3702,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I70" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="J70" s="7">
         <v>139</v>
-      </c>
-      <c t="s" r="J70" s="7">
-        <v>140</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3714,7 +3723,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3729,7 +3738,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3747,7 +3756,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3759,7 +3768,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>41</v>
@@ -3780,7 +3789,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3795,7 +3804,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3813,7 +3822,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3825,10 +3834,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I74" s="7">
+        <v>143</v>
+      </c>
+      <c t="s" r="J74" s="7">
         <v>144</v>
-      </c>
-      <c t="s" r="J74" s="7">
-        <v>145</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3861,22 +3870,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
+        <v>145</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H76" s="8">
         <v>146</v>
-      </c>
-      <c r="F76" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G76" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H76" s="8">
-        <v>147</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3894,22 +3903,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
+        <v>145</v>
+      </c>
+      <c r="F77" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G77" s="8">
         <v>146</v>
-      </c>
-      <c r="F77" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G77" s="8">
-        <v>147</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J77" s="7">
         <v>149</v>
-      </c>
-      <c t="s" r="J77" s="7">
-        <v>150</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3927,7 +3936,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3936,13 +3945,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="I78" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J78" s="7">
         <v>151</v>
-      </c>
-      <c t="s" r="J78" s="7">
-        <v>152</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3960,22 +3969,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
+        <v>145</v>
+      </c>
+      <c r="F79" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G79" s="8">
         <v>146</v>
       </c>
-      <c r="F79" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G79" s="8">
-        <v>147</v>
-      </c>
       <c t="s" r="H79" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I79" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J79" s="7">
         <v>153</v>
-      </c>
-      <c t="s" r="J79" s="7">
-        <v>154</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3993,7 +4002,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4002,13 +4011,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H80" s="8">
+        <v>154</v>
+      </c>
+      <c t="s" r="I80" s="7">
         <v>155</v>
       </c>
-      <c t="s" r="I80" s="7">
+      <c t="s" r="J80" s="7">
         <v>156</v>
-      </c>
-      <c t="s" r="J80" s="7">
-        <v>157</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4026,22 +4035,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I81" s="7">
+        <v>157</v>
+      </c>
+      <c t="s" r="J81" s="7">
         <v>158</v>
-      </c>
-      <c t="s" r="J81" s="7">
-        <v>159</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4074,22 +4083,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
+        <v>159</v>
+      </c>
+      <c r="F83" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G83" s="8">
         <v>160</v>
-      </c>
-      <c r="F83" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G83" s="8">
-        <v>161</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I83" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="J83" s="7">
         <v>162</v>
-      </c>
-      <c t="s" r="J83" s="7">
-        <v>163</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4107,7 +4116,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4119,10 +4128,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I84" s="7">
+        <v>163</v>
+      </c>
+      <c t="s" r="J84" s="7">
         <v>164</v>
-      </c>
-      <c t="s" r="J84" s="7">
-        <v>165</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4140,7 +4149,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4152,10 +4161,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4188,22 +4197,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
+        <v>166</v>
+      </c>
+      <c r="F87" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G87" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H87" s="8">
         <v>167</v>
-      </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H87" s="8">
-        <v>168</v>
       </c>
       <c t="s" r="I87" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4221,22 +4230,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
+        <v>166</v>
+      </c>
+      <c r="F88" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G88" s="8">
         <v>167</v>
       </c>
-      <c r="F88" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G88" s="8">
-        <v>168</v>
-      </c>
       <c t="s" r="H88" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I88" s="7">
+        <v>169</v>
+      </c>
+      <c t="s" r="J88" s="7">
         <v>170</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>171</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4254,7 +4263,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4266,7 +4275,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>25</v>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4299,10 +4308,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I90" s="7">
+        <v>172</v>
+      </c>
+      <c t="s" r="J90" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="J90" s="7">
-        <v>174</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4320,7 +4329,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4332,10 +4341,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4362,10 +4371,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>50</v>
@@ -4401,7 +4410,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4413,10 +4422,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I94" s="7">
+        <v>177</v>
+      </c>
+      <c t="s" r="J94" s="7">
         <v>178</v>
-      </c>
-      <c t="s" r="J94" s="7">
-        <v>179</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4434,7 +4443,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4446,10 +4455,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I95" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J95" s="7">
         <v>180</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>181</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4467,7 +4476,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4476,13 +4485,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H96" s="8">
+        <v>181</v>
+      </c>
+      <c t="s" r="I96" s="7">
         <v>182</v>
       </c>
-      <c t="s" r="I96" s="7">
+      <c t="s" r="J96" s="7">
         <v>183</v>
-      </c>
-      <c t="s" r="J96" s="7">
-        <v>184</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4500,13 +4509,13 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>26</v>
@@ -4515,7 +4524,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4548,7 +4557,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4557,10 +4566,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H99" s="8">
+        <v>186</v>
+      </c>
+      <c t="s" r="I99" s="7">
         <v>187</v>
-      </c>
-      <c t="s" r="I99" s="7">
-        <v>188</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>74</v>
@@ -4581,22 +4590,22 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
+        <v>185</v>
+      </c>
+      <c r="F100" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G100" s="8">
         <v>186</v>
-      </c>
-      <c r="F100" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G100" s="8">
-        <v>187</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4614,7 +4623,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4623,10 +4632,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H101" s="8">
+        <v>189</v>
+      </c>
+      <c t="s" r="I101" s="7">
         <v>190</v>
-      </c>
-      <c t="s" r="I101" s="7">
-        <v>191</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>24</v>
@@ -4647,22 +4656,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I102" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J102" s="7">
         <v>192</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>193</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4695,7 +4704,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4704,13 +4713,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4728,22 +4737,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>108</v>
       </c>
       <c t="s" r="I105" s="7">
+        <v>194</v>
+      </c>
+      <c t="s" r="J105" s="7">
         <v>195</v>
-      </c>
-      <c t="s" r="J105" s="7">
-        <v>196</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4761,7 +4770,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4770,13 +4779,13 @@
         <v>108</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4794,22 +4803,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4827,7 +4836,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4836,13 +4845,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4860,22 +4869,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I109" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J109" s="7">
         <v>199</v>
-      </c>
-      <c t="s" r="J109" s="7">
-        <v>200</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4908,22 +4917,22 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
+        <v>200</v>
+      </c>
+      <c r="F111" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G111" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H111" s="8">
         <v>201</v>
-      </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H111" s="8">
-        <v>202</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4941,13 +4950,13 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
+        <v>200</v>
+      </c>
+      <c r="F112" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G112" s="8">
         <v>201</v>
-      </c>
-      <c r="F112" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G112" s="8">
-        <v>202</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>26</v>
@@ -4974,7 +4983,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4986,10 +4995,10 @@
         <v>105</v>
       </c>
       <c t="s" r="I113" s="7">
+        <v>202</v>
+      </c>
+      <c t="s" r="J113" s="7">
         <v>203</v>
-      </c>
-      <c t="s" r="J113" s="7">
-        <v>204</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5003,11 +5012,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C114" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5019,10 +5028,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I114" s="7">
+        <v>205</v>
+      </c>
+      <c t="s" r="J114" s="7">
         <v>206</v>
-      </c>
-      <c t="s" r="J114" s="7">
-        <v>207</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5036,11 +5045,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C115" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5049,13 +5058,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H115" s="8">
+        <v>207</v>
+      </c>
+      <c t="s" r="I115" s="7">
         <v>208</v>
       </c>
-      <c t="s" r="I115" s="7">
+      <c t="s" r="J115" s="7">
         <v>209</v>
-      </c>
-      <c t="s" r="J115" s="7">
-        <v>210</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5088,7 +5097,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5100,7 +5109,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>36</v>
@@ -5108,7 +5117,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5119,11 +5128,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C118" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5152,11 +5161,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C119" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5165,13 +5174,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H119" s="8">
+        <v>213</v>
+      </c>
+      <c t="s" r="I119" s="7">
         <v>214</v>
       </c>
-      <c t="s" r="I119" s="7">
-        <v>215</v>
-      </c>
       <c t="s" r="J119" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5185,17 +5194,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C120" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>57</v>
@@ -5204,7 +5213,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5237,7 +5246,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5249,10 +5258,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5270,7 +5279,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5282,7 +5291,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>84</v>
@@ -5303,7 +5312,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5315,10 +5324,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5336,7 +5345,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5351,7 +5360,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5384,19 +5393,19 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
+        <v>219</v>
+      </c>
+      <c r="F127" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G127" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H127" s="8">
+        <v>134</v>
+      </c>
+      <c t="s" r="I127" s="7">
         <v>220</v>
-      </c>
-      <c r="F127" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G127" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H127" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I127" s="7">
-        <v>221</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>94</v>
@@ -5417,19 +5426,19 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>24</v>
@@ -5450,7 +5459,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5459,13 +5468,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H129" s="8">
+        <v>221</v>
+      </c>
+      <c t="s" r="I129" s="7">
+        <v>164</v>
+      </c>
+      <c t="s" r="J129" s="7">
         <v>222</v>
-      </c>
-      <c t="s" r="I129" s="7">
-        <v>165</v>
-      </c>
-      <c t="s" r="J129" s="7">
-        <v>223</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5483,22 +5492,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I130" s="7">
+        <v>223</v>
+      </c>
+      <c t="s" r="J130" s="7">
         <v>224</v>
-      </c>
-      <c t="s" r="J130" s="7">
-        <v>225</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5531,22 +5540,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
+        <v>225</v>
+      </c>
+      <c r="F132" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G132" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H132" s="8">
+        <v>201</v>
+      </c>
+      <c t="s" r="I132" s="7">
         <v>226</v>
       </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H132" s="8">
-        <v>202</v>
-      </c>
-      <c t="s" r="I132" s="7">
+      <c t="s" r="J132" s="7">
         <v>227</v>
-      </c>
-      <c t="s" r="J132" s="7">
-        <v>228</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5564,13 +5573,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>26</v>
@@ -5597,7 +5606,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5606,13 +5615,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H134" s="8">
+        <v>228</v>
+      </c>
+      <c t="s" r="I134" s="7">
+        <v>184</v>
+      </c>
+      <c t="s" r="J134" s="7">
         <v>229</v>
-      </c>
-      <c t="s" r="I134" s="7">
-        <v>185</v>
-      </c>
-      <c t="s" r="J134" s="7">
-        <v>230</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5630,22 +5639,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I135" s="7">
+        <v>230</v>
+      </c>
+      <c t="s" r="J135" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="J135" s="7">
-        <v>232</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5678,7 +5687,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5690,7 +5699,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>27</v>
@@ -5711,7 +5720,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5723,10 +5732,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5744,7 +5753,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5756,7 +5765,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>91</v>
@@ -5792,7 +5801,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5804,15 +5813,15 @@
         <v>105</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -5827,7 +5836,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5836,13 +5845,13 @@
         <v>105</v>
       </c>
       <c t="s" r="H142" s="8">
+        <v>237</v>
+      </c>
+      <c t="s" r="I142" s="7">
         <v>238</v>
       </c>
-      <c t="s" r="I142" s="7">
-        <v>239</v>
-      </c>
       <c t="s" r="J142" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5860,19 +5869,19 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>105</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>61</v>
@@ -5893,7 +5902,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5905,10 +5914,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5941,22 +5950,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
+        <v>241</v>
+      </c>
+      <c r="F146" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G146" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H146" s="8">
+        <v>146</v>
+      </c>
+      <c t="s" r="I146" s="7">
         <v>242</v>
       </c>
-      <c r="F146" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G146" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H146" s="8">
-        <v>147</v>
-      </c>
-      <c t="s" r="I146" s="7">
+      <c t="s" r="J146" s="7">
         <v>243</v>
-      </c>
-      <c t="s" r="J146" s="7">
-        <v>244</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5974,22 +5983,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6003,11 +6012,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C148" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6016,13 +6025,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6036,26 +6045,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C149" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I149" s="7">
+        <v>246</v>
+      </c>
+      <c t="s" r="J149" s="7">
         <v>247</v>
-      </c>
-      <c t="s" r="J149" s="7">
-        <v>248</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6088,7 +6097,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6103,7 +6112,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6121,7 +6130,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6133,7 +6142,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>120</v>
@@ -6154,7 +6163,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6187,7 +6196,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6220,7 +6229,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6232,10 +6241,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I155" s="7">
+        <v>249</v>
+      </c>
+      <c t="s" r="J155" s="7">
         <v>250</v>
-      </c>
-      <c t="s" r="J155" s="7">
-        <v>251</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6253,7 +6262,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6265,10 +6274,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6286,7 +6295,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6298,10 +6307,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6334,7 +6343,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6346,10 +6355,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6367,7 +6376,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6379,7 +6388,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>121</v>
@@ -6400,7 +6409,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6433,7 +6442,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6448,7 +6457,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6466,7 +6475,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6475,10 +6484,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>31</v>
@@ -6499,22 +6508,22 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
+        <v>256</v>
+      </c>
+      <c t="s" r="H164" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I164" s="7">
         <v>257</v>
       </c>
-      <c t="s" r="H164" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I164" s="7">
+      <c t="s" r="J164" s="7">
         <v>258</v>
-      </c>
-      <c t="s" r="J164" s="7">
-        <v>259</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6547,26 +6556,28 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
+        <v>259</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H166" s="8">
         <v>260</v>
-      </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H166" s="8">
-        <v>261</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
+      <c t="s" r="M166" s="7">
+        <v>261</v>
+      </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c t="s" r="A167" s="6">
@@ -6580,22 +6591,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>259</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
         <v>260</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>261</v>
-      </c>
       <c t="s" r="H167" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6613,7 +6624,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6646,7 +6657,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6658,10 +6669,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6679,7 +6690,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6691,7 +6702,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>264</v>
@@ -6712,7 +6723,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6724,7 +6735,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>265</v>
@@ -6769,7 +6780,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>267</v>
@@ -6779,7 +6790,9 @@
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>226</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
@@ -6799,13 +6812,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>100</v>
@@ -6835,13 +6848,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6865,7 +6878,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>26</v>
@@ -6874,7 +6887,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6901,7 +6914,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>106</v>
@@ -6931,13 +6944,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>79</v>
@@ -6985,7 +6998,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>90</v>
@@ -7001,7 +7014,7 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>809</v>
+        <v>134</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
@@ -7017,13 +7030,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>271</v>
+        <v>57</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7034,7 +7047,7 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>808</v>
+        <v>439</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
@@ -7047,16 +7060,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
+        <v>57</v>
+      </c>
+      <c t="s" r="H182" s="8">
         <v>271</v>
       </c>
-      <c t="s" r="H182" s="8">
-        <v>26</v>
-      </c>
       <c t="s" r="I182" s="7">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7067,7 +7080,7 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
@@ -7080,113 +7093,113 @@
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c t="s" r="A184" s="6">
-        <v>13</v>
-      </c>
-      <c r="B184" s="7">
-        <v>1127</v>
-      </c>
-      <c t="s" r="C184" s="7">
-        <v>14</v>
-      </c>
+      <c r="A184" s="6"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
       <c r="D184" s="7"/>
-      <c t="s" r="E184" s="7">
-        <v>269</v>
-      </c>
-      <c r="F184" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G184" s="8">
-        <v>57</v>
-      </c>
-      <c t="s" r="H184" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I184" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J184" s="7">
-        <v>252</v>
-      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="7"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="6"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
+      <c t="s" r="A185" s="6">
+        <v>13</v>
+      </c>
+      <c r="B185" s="7">
+        <v>776</v>
+      </c>
+      <c t="s" r="C185" s="7">
+        <v>14</v>
+      </c>
       <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-      <c r="G185" s="8"/>
-      <c r="H185" s="8"/>
-      <c r="I185" s="7"/>
-      <c r="J185" s="7"/>
+      <c t="s" r="E185" s="7">
+        <v>273</v>
+      </c>
+      <c r="F185" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G185" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H185" s="8">
+        <v>57</v>
+      </c>
+      <c t="s" r="I185" s="7">
+        <v>109</v>
+      </c>
+      <c t="s" r="J185" s="7">
+        <v>110</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c t="s" r="A186" s="6">
-        <v>13</v>
-      </c>
-      <c r="B186" s="7">
-        <v>776</v>
-      </c>
-      <c t="s" r="C186" s="7">
-        <v>14</v>
-      </c>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c t="s" r="E186" s="7">
-        <v>273</v>
-      </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="H186" s="8">
-        <v>57</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>109</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>110</v>
-      </c>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="6"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
+      <c t="s" r="A187" s="6">
+        <v>13</v>
+      </c>
+      <c r="B187" s="7">
+        <v>809</v>
+      </c>
+      <c t="s" r="C187" s="7">
+        <v>14</v>
+      </c>
       <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-      <c r="G187" s="8"/>
-      <c r="H187" s="8"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="7"/>
+      <c t="s" r="E187" s="7">
+        <v>274</v>
+      </c>
+      <c r="F187" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G187" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H187" s="8">
+        <v>275</v>
+      </c>
+      <c t="s" r="I187" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="J187" s="7">
+        <v>276</v>
+      </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c r="M187" s="7"/>
@@ -7196,7 +7209,7 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>134</v>
+        <v>808</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
@@ -7209,16 +7222,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7229,7 +7242,7 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>439</v>
+        <v>144</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
@@ -7242,16 +7255,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H189" s="8">
         <v>57</v>
       </c>
-      <c t="s" r="H189" s="8">
-        <v>275</v>
-      </c>
       <c t="s" r="I189" s="7">
-        <v>276</v>
+        <v>23</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7262,7 +7275,7 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>438</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
@@ -7275,16 +7288,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>27</v>
+        <v>251</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7326,7 +7339,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>124</v>
@@ -7358,7 +7371,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>26</v>
@@ -7400,7 +7413,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7460,7 +7473,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>24</v>
@@ -7490,7 +7503,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>26</v>
@@ -7499,7 +7512,7 @@
         <v>268</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7574,13 +7587,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7604,16 +7617,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7721,7 +7734,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>287</v>
@@ -7753,16 +7766,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7861,7 +7874,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7891,10 +7904,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7939,10 +7952,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8002,13 +8015,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="I214" s="7">
         <v>290</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8032,7 +8045,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>26</v>
@@ -8155,7 +8168,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8221,7 +8234,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8254,7 +8267,7 @@
         <v>298</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8317,10 +8330,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8398,7 +8411,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>101</v>
@@ -8545,10 +8558,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8575,10 +8588,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>307</v>
@@ -8605,7 +8618,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>26</v>
@@ -8614,7 +8627,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8644,7 +8657,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>309</v>
@@ -8677,7 +8690,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>267</v>
@@ -8722,13 +8735,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8754,16 +8767,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8790,10 +8803,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>263</v>
@@ -8820,13 +8833,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>283</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>312</v>
@@ -8856,7 +8869,7 @@
         <v>283</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>43</v>
@@ -8886,7 +8899,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>34</v>
@@ -8895,7 +8908,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8973,10 +8986,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9006,10 +9019,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9039,10 +9052,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9084,13 +9097,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>317</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9116,16 +9129,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9155,10 +9168,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9257,7 +9270,7 @@
         <v>320</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9287,7 +9300,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>321</v>
@@ -9320,7 +9333,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>309</v>
@@ -9371,11 +9384,13 @@
         <v>324</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
+      <c t="s" r="M259" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
@@ -9398,10 +9413,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>23</v>
@@ -9428,13 +9443,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>25</v>
@@ -9467,10 +9482,10 @@
         <v>323</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9503,7 +9518,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9512,10 +9527,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>118</v>
@@ -9536,13 +9551,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>57</v>
@@ -9551,7 +9566,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9569,7 +9584,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9578,13 +9593,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9602,19 +9617,19 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>27</v>
@@ -9635,7 +9650,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9644,13 +9659,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9668,19 +9683,19 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>67</v>
@@ -9716,7 +9731,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9725,13 +9740,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9749,13 +9764,13 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>26</v>
@@ -9782,7 +9797,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9794,10 +9809,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9815,7 +9830,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9827,7 +9842,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>308</v>
@@ -9848,7 +9863,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9860,10 +9875,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9881,7 +9896,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9893,10 +9908,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9929,7 +9944,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9944,7 +9959,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9962,7 +9977,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9977,7 +9992,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9995,7 +10010,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10007,10 +10022,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10028,7 +10043,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10037,7 +10052,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>77</v>
@@ -10061,13 +10076,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>26</v>
@@ -10076,7 +10091,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10109,7 +10124,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10118,7 +10133,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>48</v>
@@ -10142,19 +10157,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>75</v>
@@ -10175,7 +10190,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10184,10 +10199,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>110</v>
@@ -10208,22 +10223,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10256,13 +10271,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>57</v>
@@ -10304,13 +10319,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>57</v>
@@ -10319,7 +10334,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10337,7 +10352,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10352,7 +10367,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10370,7 +10385,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10382,7 +10397,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>102</v>
@@ -10403,7 +10418,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10415,10 +10430,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10451,7 +10466,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10466,12 +10481,12 @@
         <v>287</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10486,7 +10501,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10501,7 +10516,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10519,7 +10534,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10528,10 +10543,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>62</v>
@@ -10552,19 +10567,19 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>114</v>
@@ -10600,7 +10615,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10615,7 +10630,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10633,7 +10648,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10645,10 +10660,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10666,7 +10681,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10675,7 +10690,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I303" s="7">
         <v>121</v>
@@ -10699,13 +10714,13 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>57</v>
@@ -10747,7 +10762,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10759,7 +10774,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>120</v>
@@ -10782,7 +10797,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10791,13 +10806,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10815,19 +10830,19 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>264</v>
@@ -10863,7 +10878,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10875,14 +10890,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>282</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
-      <c r="M310" s="7"/>
+      <c t="s" r="M310" s="7">
+        <v>357</v>
+      </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
       <c t="s" r="A311" s="6">
@@ -10896,7 +10913,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10908,10 +10925,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10929,7 +10946,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10962,7 +10979,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -10977,7 +10994,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10995,7 +11012,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11007,7 +11024,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>103</v>
@@ -11043,7 +11060,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11052,18 +11069,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11078,13 +11095,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>26</v>
@@ -11093,7 +11110,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11111,7 +11128,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11123,10 +11140,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11144,7 +11161,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11156,7 +11173,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>22</v>
@@ -11177,7 +11194,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11186,13 +11203,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11210,13 +11227,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>26</v>
@@ -11225,7 +11242,7 @@
         <v>263</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11243,7 +11260,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11252,13 +11269,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11276,22 +11293,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11324,7 +11341,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11336,14 +11353,16 @@
         <v>283</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>324</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
-      <c r="M325" s="7"/>
+      <c t="s" r="M325" s="7">
+        <v>365</v>
+      </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
       <c t="s" r="A326" s="6">
@@ -11357,7 +11376,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11390,7 +11409,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11405,7 +11424,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11423,7 +11442,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11438,7 +11457,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11456,7 +11475,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11468,7 +11487,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>308</v>
@@ -11489,7 +11508,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11504,7 +11523,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11537,7 +11556,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11546,10 +11565,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>94</v>
@@ -11557,7 +11576,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -11572,19 +11591,19 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>280</v>
@@ -11605,7 +11624,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11614,13 +11633,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11638,13 +11657,13 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>57</v>
@@ -11653,7 +11672,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11686,7 +11705,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11695,10 +11714,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>267</v>
@@ -11721,19 +11740,19 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>32</v>
@@ -11754,7 +11773,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11763,13 +11782,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11787,19 +11806,19 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>307</v>
@@ -11820,7 +11839,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11829,13 +11848,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11853,22 +11872,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11901,7 +11920,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11916,12 +11935,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -11936,7 +11955,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11948,7 +11967,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>72</v>
@@ -11969,7 +11988,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -11978,10 +11997,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>101</v>
@@ -12002,22 +12021,22 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12035,7 +12054,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12044,10 +12063,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>60</v>
@@ -12068,22 +12087,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12116,7 +12135,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12128,7 +12147,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>324</v>
@@ -12136,7 +12155,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>379</v>
+        <v>194</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12151,7 +12170,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12184,7 +12203,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12196,10 +12215,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12217,7 +12236,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12226,13 +12245,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12250,19 +12269,19 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>264</v>
@@ -12283,7 +12302,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12316,7 +12335,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12328,10 +12347,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12364,7 +12383,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12373,13 +12392,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12397,13 +12416,13 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>71</v>
@@ -12430,7 +12449,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12463,7 +12482,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12496,7 +12515,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12508,10 +12527,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12544,7 +12563,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12579,7 +12598,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12594,7 +12613,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12612,7 +12631,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12624,7 +12643,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>311</v>
@@ -12645,7 +12664,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12660,7 +12679,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12678,7 +12697,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12690,10 +12709,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12711,7 +12730,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12723,7 +12742,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>107</v>
@@ -12744,7 +12763,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12756,10 +12775,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12777,7 +12796,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12792,7 +12811,7 @@
         <v>299</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12818,14 +12837,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B374" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>64</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12837,17 +12856,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>318</v>
+        <v>390</v>
       </c>
       <c t="s" r="K374" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>318</v>
+        <v>390</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -12862,7 +12881,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12895,7 +12914,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12928,7 +12947,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12943,7 +12962,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12961,7 +12980,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -12973,7 +12992,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>44</v>
@@ -13009,7 +13028,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13024,7 +13043,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13042,7 +13061,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13051,7 +13070,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>95</v>
@@ -13075,22 +13094,22 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13108,7 +13127,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13120,7 +13139,7 @@
         <v>323</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>50</v>
@@ -13156,7 +13175,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13168,17 +13187,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>93</v>
       </c>
       <c t="s" r="K385" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>334</v>
+        <v>393</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13193,7 +13212,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13205,10 +13224,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13226,7 +13245,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13238,10 +13257,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13259,7 +13278,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13274,7 +13293,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13292,7 +13311,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13304,10 +13323,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13340,7 +13359,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13349,13 +13368,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13373,13 +13392,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>57</v>
@@ -13406,7 +13425,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13439,7 +13458,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13451,10 +13470,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13472,7 +13491,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13484,10 +13503,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13520,7 +13539,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13529,13 +13548,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13553,22 +13572,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13586,7 +13605,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13598,10 +13617,10 @@
         <v>52</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13619,7 +13638,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13634,7 +13653,7 @@
         <v>280</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13652,7 +13671,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13664,7 +13683,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>299</v>
@@ -13700,13 +13719,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>105</v>
@@ -13715,14 +13734,14 @@
         <v>114</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="K403" s="7">
         <v>68</v>
       </c>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -13737,7 +13756,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13746,20 +13765,20 @@
         <v>105</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13774,13 +13793,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>105</v>
@@ -13789,7 +13808,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13822,7 +13841,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13831,7 +13850,7 @@
         <v>105</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>47</v>
@@ -13842,7 +13861,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>400</v>
+        <v>128</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -13857,13 +13876,13 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>105</v>
@@ -13872,7 +13891,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13905,7 +13924,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -13917,7 +13936,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>24</v>
@@ -13938,7 +13957,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -13947,13 +13966,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>313</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13986,7 +14005,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14019,7 +14038,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14034,7 +14053,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14052,7 +14071,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14061,10 +14080,10 @@
         <v>105</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>114</v>
@@ -14100,7 +14119,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14109,13 +14128,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14133,13 +14152,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>26</v>
@@ -14181,7 +14200,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14196,7 +14215,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14214,7 +14233,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14237,7 +14256,7 @@
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c t="s" r="A422" s="9">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
@@ -14257,7 +14276,7 @@
     <row r="423" ht="65.25" customHeight="1"/>
     <row r="424" ht="16.5" customHeight="1">
       <c t="s" r="A424" s="10">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B424" s="10"/>
       <c r="C424" s="10"/>
@@ -14270,7 +14289,7 @@
       <c r="J424" s="10"/>
       <c r="K424" s="10"/>
       <c t="s" r="L424" s="11">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M424" s="11"/>
       <c r="N424" s="11"/>

--- a/Data/FlightPlan/FPL_06OCT26.xlsx
+++ b/Data/FlightPlan/FPL_06OCT26.xlsx
@@ -236,336 +236,348 @@
     <t>10:20</t>
   </si>
   <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:38</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
     <t>10:28</t>
   </si>
   <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:38</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>08:46</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -716,6 +728,9 @@
     <t>09:35</t>
   </si>
   <si>
+    <t>12:51</t>
+  </si>
+  <si>
     <t>13:30</t>
   </si>
   <si>
@@ -803,7 +818,7 @@
     <t>09:08</t>
   </si>
   <si>
-    <t>10:57</t>
+    <t>11:02</t>
   </si>
   <si>
     <t>17:30</t>
@@ -848,138 +863,150 @@
     <t>11:23</t>
   </si>
   <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
     <t>BKK</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>19:50</t>
-  </si>
-  <si>
     <t>22:00</t>
   </si>
   <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:16</t>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>13:40</t>
   </si>
   <si>
     <t>16:10</t>
   </si>
   <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
     <t>21:45</t>
   </si>
   <si>
@@ -1019,9 +1046,6 @@
     <t>16:55</t>
   </si>
   <si>
-    <t>17:55</t>
-  </si>
-  <si>
     <t>VN-A648</t>
   </si>
   <si>
@@ -1094,7 +1118,7 @@
     <t>08:25</t>
   </si>
   <si>
-    <t>23:40</t>
+    <t>22:10</t>
   </si>
   <si>
     <t>VN-A658</t>
@@ -1106,6 +1130,9 @@
     <t>11:50</t>
   </si>
   <si>
+    <t>11:48</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1124,9 +1151,6 @@
     <t>13:33</t>
   </si>
   <si>
-    <t>17:40</t>
-  </si>
-  <si>
     <t>VN-A667</t>
   </si>
   <si>
@@ -1190,45 +1214,48 @@
     <t>10:36</t>
   </si>
   <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
     <t>VCL</t>
   </si>
   <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
     <t>05:20</t>
   </si>
   <si>
-    <t>16:00</t>
-  </si>
-  <si>
     <t>21:35</t>
   </si>
   <si>
@@ -1241,9 +1268,6 @@
     <t>10:11</t>
   </si>
   <si>
-    <t>22:10</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1271,6 +1295,9 @@
     <t>10:35</t>
   </si>
   <si>
+    <t>10:41</t>
+  </si>
+  <si>
     <t>24 *</t>
   </si>
   <si>
@@ -1295,6 +1322,9 @@
     <t>VN-A698</t>
   </si>
   <si>
+    <t>14:22</t>
+  </si>
+  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1349,7 +1379,7 @@
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 06, 2026 09:36</t>
+    <t xml:space="preserve">Generated on  Oct 06, 2026 10:00</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2744,7 +2774,9 @@
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
+      <c t="s" r="M34" s="7">
+        <v>88</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c t="s" r="A35" s="6">
@@ -2767,13 +2799,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I35" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2797,16 +2829,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2839,7 +2871,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2851,15 +2883,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -2874,7 +2906,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2886,10 +2918,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2907,7 +2939,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2919,10 +2951,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2940,7 +2972,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2952,10 +2984,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2988,7 +3020,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3000,15 +3032,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -3023,7 +3055,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3056,7 +3088,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3068,10 +3100,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3104,22 +3136,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3137,7 +3169,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3146,13 +3178,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3170,22 +3202,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3218,7 +3250,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3227,18 +3259,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3253,27 +3285,27 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3288,7 +3320,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3297,18 +3329,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3323,13 +3355,13 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>26</v>
@@ -3338,7 +3370,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3356,7 +3388,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3365,10 +3397,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>79</v>
@@ -3389,22 +3421,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3422,7 +3454,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3434,10 +3466,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3455,7 +3487,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3467,10 +3499,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3503,7 +3535,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3515,7 +3547,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J60" s="7">
         <v>37</v>
@@ -3538,7 +3570,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3550,14 +3582,16 @@
         <v>59</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
+      <c t="s" r="M61" s="7">
+        <v>138</v>
+      </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c t="s" r="A62" s="6">
@@ -3571,7 +3605,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3583,10 +3617,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3604,7 +3638,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3616,10 +3650,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3652,7 +3686,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3661,18 +3695,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3687,19 +3721,19 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>81</v>
@@ -3720,7 +3754,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3732,10 +3766,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3768,7 +3802,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3783,7 +3817,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3803,7 +3837,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3815,15 +3849,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -3838,7 +3872,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3853,7 +3887,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3871,7 +3905,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3883,7 +3917,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>42</v>
@@ -3904,7 +3938,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3916,10 +3950,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3937,7 +3971,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3949,10 +3983,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3985,7 +4019,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3994,18 +4028,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4020,22 +4054,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4053,7 +4087,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4062,13 +4096,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4086,22 +4120,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4119,7 +4153,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4128,13 +4162,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4152,22 +4186,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4200,27 +4234,27 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4235,7 +4269,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4247,10 +4281,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4268,7 +4302,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4280,10 +4314,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4316,7 +4350,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4325,17 +4359,19 @@
         <v>26</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
+      <c t="s" r="M87" s="7">
+        <v>180</v>
+      </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c t="s" r="A88" s="6">
@@ -4349,22 +4385,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4382,7 +4418,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4397,7 +4433,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4415,7 +4451,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4427,10 +4463,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4463,27 +4499,27 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>75</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4498,7 +4534,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4507,10 +4543,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>87</v>
@@ -4531,22 +4567,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4564,7 +4600,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4579,7 +4615,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4597,7 +4633,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4609,10 +4645,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4630,7 +4666,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4642,10 +4678,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4678,7 +4714,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4687,10 +4723,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>77</v>
@@ -4711,22 +4747,22 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4744,7 +4780,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4753,10 +4789,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>24</v>
@@ -4777,22 +4813,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4810,7 +4846,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4819,10 +4855,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>51</v>
@@ -4858,7 +4894,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4867,13 +4903,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4893,27 +4929,27 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -4928,22 +4964,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4961,22 +4997,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4994,7 +5030,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5003,13 +5039,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5027,22 +5063,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5075,7 +5111,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5084,18 +5120,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5110,22 +5146,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5143,7 +5179,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5152,13 +5188,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5172,26 +5208,26 @@
         <v>7706</v>
       </c>
       <c t="s" r="C115" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5205,11 +5241,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C116" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5218,13 +5254,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5257,7 +5293,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5266,10 +5302,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>36</v>
@@ -5277,7 +5313,7 @@
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5288,26 +5324,26 @@
         <v>5068</v>
       </c>
       <c t="s" r="C119" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5321,11 +5357,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C120" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5334,13 +5370,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5354,26 +5390,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C121" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5406,7 +5442,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5418,15 +5454,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5441,7 +5477,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5453,10 +5489,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5474,7 +5510,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5486,10 +5522,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5507,7 +5543,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5519,10 +5555,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5555,7 +5591,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5564,17 +5600,19 @@
         <v>26</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c t="s" r="M128" s="7">
+        <v>239</v>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
@@ -5588,19 +5626,19 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>24</v>
@@ -5621,7 +5659,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5630,13 +5668,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5654,22 +5692,22 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
+        <v>241</v>
+      </c>
+      <c t="s" r="H131" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I131" s="7">
         <v>236</v>
       </c>
-      <c t="s" r="H131" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I131" s="7">
-        <v>232</v>
-      </c>
       <c t="s" r="J131" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5702,7 +5740,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5711,13 +5749,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5737,19 +5775,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>43</v>
@@ -5770,7 +5808,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5779,13 +5817,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5803,22 +5841,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5851,7 +5889,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5863,7 +5901,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>27</v>
@@ -5884,7 +5922,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5896,10 +5934,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5917,7 +5955,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5929,10 +5967,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5965,7 +6003,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5974,18 +6012,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6000,22 +6038,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6033,19 +6071,19 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>63</v>
@@ -6066,22 +6104,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6114,7 +6152,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6123,18 +6161,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6149,22 +6187,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6178,11 +6216,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C149" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6191,13 +6229,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6211,26 +6249,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C150" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6263,7 +6301,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6278,12 +6316,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6298,7 +6336,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6310,15 +6348,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6333,7 +6371,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6348,7 +6386,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6366,7 +6404,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6381,7 +6419,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6399,7 +6437,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6411,10 +6449,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6432,7 +6470,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6444,10 +6482,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6465,7 +6503,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6477,10 +6515,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6513,7 +6551,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6525,10 +6563,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6546,7 +6584,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6558,10 +6596,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6579,7 +6617,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6591,7 +6629,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>23</v>
@@ -6612,7 +6650,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6627,7 +6665,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6645,7 +6683,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6654,10 +6692,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>31</v>
@@ -6678,22 +6716,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6726,7 +6764,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6735,18 +6773,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6761,27 +6799,27 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6789,14 +6827,14 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>807</v>
+        <v>138</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6805,13 +6843,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>279</v>
+        <v>59</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6822,29 +6860,29 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>800</v>
+        <v>147</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>279</v>
+        <v>59</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>187</v>
+        <v>285</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6855,14 +6893,14 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>642</v>
+        <v>154</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6871,13 +6909,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>281</v>
+        <v>144</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6888,29 +6926,29 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>643</v>
+        <v>163</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6943,7 +6981,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6952,18 +6990,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -6978,27 +7016,27 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7013,7 +7051,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7022,13 +7060,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7046,13 +7084,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>26</v>
@@ -7061,7 +7099,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7079,7 +7117,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7088,13 +7126,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7112,19 +7150,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>82</v>
@@ -7160,7 +7198,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7172,15 +7210,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7195,7 +7233,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7207,10 +7245,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7228,7 +7266,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7240,7 +7278,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>43</v>
@@ -7261,7 +7299,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7273,10 +7311,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7294,7 +7332,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7306,10 +7344,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7327,7 +7365,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7339,7 +7377,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>63</v>
@@ -7375,7 +7413,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7408,7 +7446,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7420,10 +7458,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7441,7 +7479,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7450,13 +7488,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7474,22 +7512,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7507,7 +7545,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7516,13 +7554,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7540,22 +7578,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7588,26 +7626,30 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>114</v>
-      </c>
-      <c r="K195" s="7"/>
+        <v>115</v>
+      </c>
+      <c t="s" r="K195" s="7">
+        <v>271</v>
+      </c>
       <c r="L195" s="7"/>
-      <c r="M195" s="7"/>
+      <c t="s" r="M195" s="7">
+        <v>302</v>
+      </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="6"/>
@@ -7636,7 +7678,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7645,18 +7687,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7671,13 +7713,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>26</v>
@@ -7704,7 +7746,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7716,7 +7758,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>25</v>
@@ -7737,7 +7779,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7749,10 +7791,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7770,7 +7812,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7782,10 +7824,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7818,7 +7860,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7827,10 +7869,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>49</v>
@@ -7838,7 +7880,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -7853,13 +7895,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>26</v>
@@ -7868,12 +7910,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -7881,14 +7923,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>636</v>
+        <v>807</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7897,13 +7939,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>73</v>
+        <v>314</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7914,29 +7956,29 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>633</v>
+        <v>800</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>73</v>
+        <v>314</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>309</v>
+        <v>191</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7947,14 +7989,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>394</v>
+        <v>642</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7963,13 +8005,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7980,29 +8022,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>395</v>
+        <v>643</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>286</v>
+        <v>164</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8035,7 +8077,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8050,12 +8092,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8070,7 +8112,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8079,13 +8121,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8103,22 +8145,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
+        <v>317</v>
+      </c>
+      <c r="F212" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G212" s="8">
         <v>310</v>
-      </c>
-      <c r="F212" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G212" s="8">
-        <v>305</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8136,7 +8178,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8145,17 +8187,21 @@
         <v>73</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>78</v>
       </c>
-      <c r="K213" s="7"/>
+      <c t="s" r="K213" s="7">
+        <v>128</v>
+      </c>
       <c r="L213" s="7"/>
-      <c r="M213" s="7"/>
+      <c t="s" r="M213" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
@@ -8169,26 +8215,30 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>43</v>
       </c>
-      <c r="K214" s="7"/>
+      <c t="s" r="K214" s="7">
+        <v>235</v>
+      </c>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="6"/>
@@ -8217,7 +8267,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8226,10 +8276,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>37</v>
@@ -8237,7 +8287,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8252,27 +8302,27 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8287,7 +8337,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8296,13 +8346,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8320,19 +8370,19 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>79</v>
@@ -8353,7 +8403,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8362,13 +8412,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8386,22 +8436,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8434,7 +8484,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8443,18 +8493,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8469,13 +8519,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>26</v>
@@ -8502,7 +8552,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8511,13 +8561,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8535,22 +8585,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8568,7 +8618,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8577,13 +8627,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8601,22 +8651,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8649,7 +8699,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8661,15 +8711,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8684,7 +8734,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8693,10 +8743,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>44</v>
@@ -8717,22 +8767,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8750,7 +8800,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8762,10 +8812,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8798,7 +8848,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8807,18 +8857,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -8833,22 +8883,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8866,7 +8916,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8875,10 +8925,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>23</v>
@@ -8899,19 +8949,19 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>25</v>
@@ -8932,7 +8982,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8941,13 +8991,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8980,7 +9030,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8992,7 +9042,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>52</v>
@@ -9000,7 +9050,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9015,7 +9065,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9027,15 +9077,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>257</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9050,7 +9100,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9059,13 +9109,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9083,22 +9133,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9116,7 +9166,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9128,10 +9178,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9149,7 +9199,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9161,10 +9211,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9197,7 +9247,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9206,18 +9256,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9232,22 +9282,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9265,7 +9315,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9274,13 +9324,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9298,22 +9348,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9331,22 +9381,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9364,22 +9414,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9412,7 +9462,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9427,12 +9477,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9447,7 +9497,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9459,10 +9509,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9480,7 +9530,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9492,10 +9542,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9513,7 +9563,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9525,10 +9575,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9561,7 +9611,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9570,18 +9620,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9596,27 +9646,27 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9631,7 +9681,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9643,10 +9693,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9664,7 +9714,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9676,10 +9726,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9697,7 +9747,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9706,13 +9756,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9730,22 +9780,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9778,27 +9828,27 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -9813,7 +9863,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9822,10 +9872,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>31</v>
@@ -9846,22 +9896,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9894,7 +9944,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9903,18 +9953,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -9929,27 +9979,27 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -9964,7 +10014,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9973,13 +10023,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9997,19 +10047,19 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>27</v>
@@ -10030,7 +10080,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10039,13 +10089,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10063,19 +10113,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>69</v>
@@ -10111,7 +10161,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10120,18 +10170,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10146,40 +10196,42 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>19</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
-      <c r="M279" s="7"/>
+      <c t="s" r="M279" s="7">
+        <v>262</v>
+      </c>
     </row>
     <row r="280" ht="15" customHeight="1">
       <c t="s" r="A280" s="6">
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>138</v>
+        <v>636</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10188,13 +10240,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10205,29 +10257,29 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>147</v>
+        <v>633</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10238,14 +10290,14 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10254,13 +10306,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>59</v>
+        <v>310</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>199</v>
+        <v>322</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10271,29 +10323,29 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>59</v>
+        <v>310</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10326,7 +10378,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10338,15 +10390,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10361,7 +10413,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10373,14 +10425,16 @@
         <v>59</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
-      <c r="M286" s="7"/>
+      <c t="s" r="M286" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
       <c t="s" r="A287" s="6">
@@ -10394,7 +10448,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10406,10 +10460,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10427,7 +10481,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10436,13 +10490,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10460,13 +10514,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>26</v>
@@ -10475,7 +10529,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10508,7 +10562,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10517,7 +10571,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>49</v>
@@ -10528,7 +10582,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10543,19 +10597,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>78</v>
@@ -10576,7 +10630,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10585,13 +10639,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10609,22 +10663,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10657,13 +10711,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>59</v>
@@ -10672,12 +10726,12 @@
         <v>55</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10692,7 +10746,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10707,7 +10761,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10725,7 +10779,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10737,7 +10791,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>45</v>
@@ -10773,27 +10827,27 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -10808,7 +10862,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10817,13 +10871,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10841,22 +10895,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10889,7 +10943,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10901,15 +10955,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -10924,7 +10978,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10936,15 +10990,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -10959,7 +11013,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10968,10 +11022,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>64</v>
@@ -10992,22 +11046,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11040,7 +11094,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11052,15 +11106,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11075,7 +11129,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11087,10 +11141,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11108,7 +11162,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11117,10 +11171,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>79</v>
@@ -11141,22 +11195,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11189,7 +11243,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11201,15 +11255,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11224,7 +11278,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11236,10 +11290,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11257,7 +11311,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11269,10 +11323,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11290,7 +11344,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11302,10 +11356,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11323,7 +11377,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11335,10 +11389,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11371,7 +11425,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11383,15 +11437,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11406,7 +11460,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11418,10 +11472,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11439,7 +11493,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11454,7 +11508,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11472,7 +11526,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11487,7 +11541,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11505,7 +11559,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11517,10 +11571,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11553,7 +11607,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11562,18 +11616,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -11588,27 +11642,27 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11623,7 +11677,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11635,15 +11689,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11658,7 +11712,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11670,7 +11724,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>22</v>
@@ -11684,14 +11738,14 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11700,13 +11754,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>393</v>
+        <v>198</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>241</v>
+        <v>99</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11717,29 +11771,29 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>393</v>
+        <v>198</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>280</v>
+        <v>401</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>231</v>
+        <v>344</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11757,7 +11811,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11766,13 +11820,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11790,22 +11844,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11838,7 +11892,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11847,18 +11901,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -11873,26 +11927,28 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>86</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>406</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
@@ -11906,7 +11962,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11921,11 +11977,15 @@
         <v>77</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>178</v>
-      </c>
-      <c r="K337" s="7"/>
+        <v>181</v>
+      </c>
+      <c t="s" r="K337" s="7">
+        <v>275</v>
+      </c>
       <c r="L337" s="7"/>
-      <c r="M337" s="7"/>
+      <c t="s" r="M337" s="7">
+        <v>128</v>
+      </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
@@ -11939,7 +11999,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11954,11 +12014,15 @@
         <v>42</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>230</v>
-      </c>
-      <c r="K338" s="7"/>
+        <v>234</v>
+      </c>
+      <c t="s" r="K338" s="7">
+        <v>99</v>
+      </c>
       <c r="L338" s="7"/>
-      <c r="M338" s="7"/>
+      <c t="s" r="M338" s="7">
+        <v>235</v>
+      </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
@@ -11972,7 +12036,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11981,17 +12045,21 @@
         <v>59</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>336</v>
-      </c>
-      <c r="K339" s="7"/>
+        <v>285</v>
+      </c>
+      <c t="s" r="K339" s="7">
+        <v>24</v>
+      </c>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>162</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c t="s" r="A340" s="6">
@@ -12005,13 +12073,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>34</v>
@@ -12020,7 +12088,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12053,7 +12121,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12062,18 +12130,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12088,22 +12156,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12121,7 +12189,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12130,13 +12198,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12154,22 +12222,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12202,7 +12270,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12211,18 +12279,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12237,19 +12305,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>32</v>
@@ -12265,14 +12333,14 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12281,13 +12349,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>194</v>
+        <v>413</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12298,29 +12366,29 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>194</v>
+        <v>413</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>405</v>
+        <v>315</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>335</v>
+        <v>235</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12338,7 +12406,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12347,13 +12415,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12371,22 +12439,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12419,7 +12487,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12431,15 +12499,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12454,7 +12522,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12466,7 +12534,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>74</v>
@@ -12474,7 +12542,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12489,7 +12557,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12498,13 +12566,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12522,22 +12590,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12548,14 +12616,14 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>282</v>
+        <v>394</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12564,13 +12632,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>371</v>
+        <v>24</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12581,29 +12649,29 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>283</v>
+        <v>395</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>410</v>
+        <v>163</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12636,7 +12704,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12648,15 +12716,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12671,7 +12739,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12683,10 +12751,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12704,7 +12772,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12716,10 +12784,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12737,7 +12805,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12749,10 +12817,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12785,7 +12853,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12794,13 +12862,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12818,13 +12886,13 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>73</v>
@@ -12833,7 +12901,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12851,7 +12919,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12884,7 +12952,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12896,7 +12964,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>81</v>
@@ -12917,7 +12985,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12929,10 +12997,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12965,7 +13033,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12980,12 +13048,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13000,7 +13068,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13015,12 +13083,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13035,7 +13103,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13047,14 +13115,16 @@
         <v>54</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
-      <c r="M374" s="7"/>
+      <c t="s" r="M374" s="7">
+        <v>428</v>
+      </c>
     </row>
     <row r="375" ht="15" customHeight="1">
       <c t="s" r="A375" s="6">
@@ -13068,7 +13138,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13080,10 +13150,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13109,14 +13179,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B377" s="7">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>66</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13128,17 +13198,17 @@
         <v>59</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13153,7 +13223,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13162,20 +13232,20 @@
         <v>59</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="K378" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13190,29 +13260,29 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13242,27 +13312,27 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13277,7 +13347,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13286,13 +13356,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13310,19 +13380,19 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>27</v>
@@ -13343,7 +13413,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13352,10 +13422,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>51</v>
@@ -13391,7 +13461,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13403,13 +13473,13 @@
         <v>26</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="K386" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
@@ -13428,7 +13498,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13437,13 +13507,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13461,22 +13531,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13494,7 +13564,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13506,10 +13576,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13527,7 +13597,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13539,10 +13609,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13575,7 +13645,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13584,17 +13654,19 @@
         <v>59</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>437</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
@@ -13608,13 +13680,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>59</v>
@@ -13623,7 +13695,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13641,7 +13713,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13656,7 +13728,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13674,7 +13746,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13686,10 +13758,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13707,7 +13779,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13719,10 +13791,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13755,7 +13827,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13764,18 +13836,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -13790,22 +13862,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13823,7 +13895,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13835,10 +13907,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13856,7 +13928,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13868,10 +13940,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13889,7 +13961,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13901,10 +13973,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13937,29 +14009,29 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c t="s" r="K404" s="7">
         <v>70</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13974,29 +14046,29 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14011,29 +14083,29 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14063,16 +14135,16 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>48</v>
@@ -14083,7 +14155,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14098,22 +14170,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14146,7 +14218,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14158,7 +14230,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>24</v>
@@ -14179,7 +14251,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14188,13 +14260,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14227,26 +14299,28 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>55</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
-      <c r="M414" s="7"/>
+      <c t="s" r="M414" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c t="s" r="A415" s="6">
@@ -14260,7 +14334,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14269,13 +14343,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14293,22 +14367,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14341,7 +14415,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14350,13 +14424,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14374,22 +14448,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14422,7 +14496,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14434,10 +14508,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14455,7 +14529,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14467,10 +14541,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14478,7 +14552,7 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c t="s" r="A423" s="9">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
@@ -14498,7 +14572,7 @@
     <row r="424" ht="65.25" customHeight="1"/>
     <row r="425" ht="17.25" customHeight="1">
       <c t="s" r="A425" s="10">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="B425" s="10"/>
       <c r="C425" s="10"/>
@@ -14511,7 +14585,7 @@
       <c r="J425" s="10"/>
       <c r="K425" s="10"/>
       <c t="s" r="L425" s="11">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="M425" s="11"/>
       <c r="N425" s="11"/>

--- a/Data/FlightPlan/FPL_06OCT26.xlsx
+++ b/Data/FlightPlan/FPL_06OCT26.xlsx
@@ -92,7 +92,7 @@
     <t>18:25</t>
   </si>
   <si>
-    <t>18:17</t>
+    <t>18:31</t>
   </si>
   <si>
     <t>SGN</t>
@@ -473,6 +473,9 @@
     <t>15:40</t>
   </si>
   <si>
+    <t>18:04</t>
+  </si>
+  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -581,7 +584,7 @@
     <t>15:30</t>
   </si>
   <si>
-    <t>19:33</t>
+    <t>19:53</t>
   </si>
   <si>
     <t>19:00</t>
@@ -620,6 +623,9 @@
     <t>18:05</t>
   </si>
   <si>
+    <t>17:54</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
@@ -791,6 +797,9 @@
     <t>16:05</t>
   </si>
   <si>
+    <t>17:29</t>
+  </si>
+  <si>
     <t>20:05</t>
   </si>
   <si>
@@ -1007,324 +1016,339 @@
     <t>14:36</t>
   </si>
   <si>
+    <t>17:42</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:44</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>16:16</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>09:48</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>18:32</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>DYG</t>
+  </si>
+  <si>
+    <t>20:26</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
     <t>17:33</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>11:29</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>12:58</t>
-  </si>
-  <si>
-    <t>16:16</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:54</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:13</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>17:23</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:59</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>09:48</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>18:32</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>17:03</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>DYG</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1406,6 +1430,9 @@
     <t>CMB</t>
   </si>
   <si>
+    <t>22:15</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1532,9 +1559,6 @@
     <t>VN-A697</t>
   </si>
   <si>
-    <t>17:35</t>
-  </si>
-  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1613,7 +1637,7 @@
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 06, 2026 15:55</t>
+    <t xml:space="preserve">Generated on  Oct 06, 2026 16:10</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3950,7 +3974,9 @@
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
+      <c t="s" r="M64" s="7">
+        <v>154</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="6"/>
@@ -3979,7 +4005,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3988,7 +4014,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="I66" s="7">
         <v>148</v>
@@ -3999,7 +4025,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4014,13 +4040,13 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>64</v>
@@ -4034,7 +4060,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4049,7 +4075,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4064,7 +4090,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4097,7 +4123,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4112,7 +4138,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -4132,7 +4158,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4144,15 +4170,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4167,7 +4193,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4182,12 +4208,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4202,7 +4228,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4214,7 +4240,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>44</v>
@@ -4222,7 +4248,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4237,7 +4263,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4252,7 +4278,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4270,7 +4296,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4285,7 +4311,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -4303,7 +4329,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4315,10 +4341,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4351,7 +4377,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4360,18 +4386,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4386,27 +4412,27 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4421,7 +4447,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4430,18 +4456,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4456,13 +4482,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>28</v>
@@ -4471,7 +4497,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4489,7 +4515,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4522,7 +4548,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4537,7 +4563,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4570,27 +4596,27 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4605,7 +4631,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4617,17 +4643,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K86" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4642,7 +4668,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4654,17 +4680,17 @@
         <v>64</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>99</v>
       </c>
       <c t="s" r="K87" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4679,7 +4705,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4691,10 +4717,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4727,7 +4753,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4736,18 +4762,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="I90" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4762,27 +4788,27 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4797,7 +4823,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4812,11 +4838,13 @@
         <v>23</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
+      <c t="s" r="M92" s="7">
+        <v>204</v>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c t="s" r="A93" s="6">
@@ -4830,7 +4858,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4845,7 +4873,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4878,7 +4906,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4890,15 +4918,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4913,7 +4941,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4925,7 +4953,7 @@
         <v>120</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>94</v>
@@ -4933,7 +4961,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4948,7 +4976,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4960,10 +4988,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4981,7 +5009,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4996,7 +5024,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5014,7 +5042,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5026,10 +5054,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5047,7 +5075,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5059,10 +5087,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5095,7 +5123,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5104,10 +5132,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>82</v>
@@ -5115,7 +5143,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5130,27 +5158,27 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5165,7 +5193,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5185,7 +5213,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5200,7 +5228,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5212,10 +5240,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5233,7 +5261,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5242,10 +5270,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>54</v>
@@ -5281,7 +5309,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5290,13 +5318,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5316,27 +5344,27 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>123</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5351,7 +5379,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5360,18 +5388,18 @@
         <v>123</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5386,27 +5414,27 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5421,7 +5449,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5430,10 +5458,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>100</v>
@@ -5454,22 +5482,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5502,7 +5530,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5511,18 +5539,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5537,13 +5565,13 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>28</v>
@@ -5557,7 +5585,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5572,7 +5600,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5584,10 +5612,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5601,11 +5629,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C118" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5617,7 +5645,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>102</v>
@@ -5634,11 +5662,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C119" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5647,13 +5675,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5686,7 +5714,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5698,7 +5726,7 @@
         <v>120</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>38</v>
@@ -5706,7 +5734,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5717,11 +5745,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C122" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5741,7 +5769,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5752,11 +5780,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C123" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5765,13 +5793,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5785,26 +5813,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C124" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5837,7 +5865,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5849,15 +5877,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5872,7 +5900,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5884,15 +5912,15 @@
         <v>78</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5907,7 +5935,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5919,14 +5947,16 @@
         <v>64</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>122</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c t="s" r="M128" s="7">
+        <v>262</v>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
@@ -5940,7 +5970,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5952,10 +5982,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5988,7 +6018,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5997,10 +6027,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>108</v>
@@ -6008,7 +6038,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6023,19 +6053,19 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>25</v>
@@ -6043,7 +6073,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6058,7 +6088,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6067,13 +6097,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6091,22 +6121,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -6139,7 +6169,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6148,13 +6178,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6174,13 +6204,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>28</v>
@@ -6194,7 +6224,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6209,7 +6239,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6218,13 +6248,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6242,22 +6272,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6290,7 +6320,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6302,7 +6332,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>29</v>
@@ -6310,7 +6340,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6325,7 +6355,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6337,7 +6367,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>102</v>
@@ -6358,7 +6388,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6370,7 +6400,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>105</v>
@@ -6406,7 +6436,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6418,15 +6448,15 @@
         <v>120</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6441,7 +6471,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6450,18 +6480,18 @@
         <v>120</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6476,19 +6506,19 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>120</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>68</v>
@@ -6509,7 +6539,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6521,10 +6551,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6557,7 +6587,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6566,18 +6596,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6592,27 +6622,27 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6623,11 +6653,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C152" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6636,13 +6666,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6656,26 +6686,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6708,7 +6738,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6723,12 +6753,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6743,7 +6773,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6755,7 +6785,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>136</v>
@@ -6763,7 +6793,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6778,7 +6808,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6798,7 +6828,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6813,7 +6843,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6833,7 +6863,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6848,7 +6878,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6860,10 +6890,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6881,7 +6911,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6893,10 +6923,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6929,7 +6959,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6941,15 +6971,15 @@
         <v>78</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6964,7 +6994,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6976,7 +7006,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>139</v>
@@ -6984,7 +7014,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6999,7 +7029,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7034,7 +7064,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7049,7 +7079,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -7067,7 +7097,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7076,10 +7106,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>33</v>
@@ -7100,22 +7130,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7148,7 +7178,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7157,18 +7187,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="I169" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7183,27 +7213,27 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7218,7 +7248,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7230,15 +7260,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7253,7 +7283,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7265,10 +7295,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7301,7 +7331,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7313,15 +7343,15 @@
         <v>96</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7336,7 +7366,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7348,7 +7378,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>113</v>
@@ -7371,7 +7401,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7380,18 +7410,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7406,13 +7436,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>28</v>
@@ -7421,12 +7451,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7441,7 +7471,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7450,7 +7480,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>121</v>
@@ -7474,19 +7504,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>89</v>
@@ -7522,7 +7552,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7534,7 +7564,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>104</v>
@@ -7542,7 +7572,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7557,7 +7587,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7569,15 +7599,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7592,7 +7622,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7604,7 +7634,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>45</v>
@@ -7612,7 +7642,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7627,7 +7657,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7642,7 +7672,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7660,7 +7690,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7672,10 +7702,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7693,7 +7723,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7705,7 +7735,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>68</v>
@@ -7741,7 +7771,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7761,7 +7791,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7776,7 +7806,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7788,15 +7818,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7811,7 +7841,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7820,18 +7850,18 @@
         <v>64</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7846,22 +7876,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7879,7 +7909,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7888,7 +7918,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>145</v>
@@ -7912,22 +7942,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7960,7 +7990,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7978,11 +8008,11 @@
         <v>125</v>
       </c>
       <c t="s" r="K195" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8012,7 +8042,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8021,18 +8051,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8047,13 +8077,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>28</v>
@@ -8067,7 +8097,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8082,7 +8112,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8094,7 +8124,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>26</v>
@@ -8115,7 +8145,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8127,7 +8157,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>144</v>
@@ -8148,7 +8178,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8160,10 +8190,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8196,7 +8226,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8205,7 +8235,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>147</v>
@@ -8216,7 +8246,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8231,13 +8261,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>28</v>
@@ -8246,12 +8276,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8266,7 +8296,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8275,18 +8305,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8301,26 +8331,28 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c r="M206" s="7"/>
+      <c t="s" r="M206" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="6"/>
@@ -8349,7 +8381,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8364,7 +8396,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8384,7 +8416,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8393,7 +8425,7 @@
         <v>78</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>113</v>
@@ -8404,7 +8436,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8419,27 +8451,27 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8454,7 +8486,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8463,10 +8495,10 @@
         <v>78</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>83</v>
@@ -8491,29 +8523,29 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>45</v>
       </c>
       <c t="s" r="K212" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8543,7 +8575,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8552,10 +8584,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>39</v>
@@ -8563,7 +8595,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8578,27 +8610,27 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8613,7 +8645,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8622,7 +8654,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>19</v>
@@ -8633,7 +8665,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8648,13 +8680,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>64</v>
@@ -8668,7 +8700,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8683,7 +8715,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8698,7 +8730,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8716,7 +8748,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8728,10 +8760,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8764,7 +8796,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8776,15 +8808,15 @@
         <v>123</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8799,7 +8831,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8819,7 +8851,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8834,7 +8866,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8843,10 +8875,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>153</v>
@@ -8854,7 +8886,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8869,19 +8901,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>141</v>
@@ -8902,7 +8934,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8914,7 +8946,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>99</v>
@@ -8935,7 +8967,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8947,10 +8979,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8983,7 +9015,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8998,12 +9030,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9018,7 +9050,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9027,7 +9059,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>110</v>
@@ -9038,7 +9070,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9053,22 +9085,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -9086,7 +9118,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9098,10 +9130,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9134,7 +9166,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9143,18 +9175,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9169,19 +9201,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>114</v>
@@ -9204,7 +9236,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9213,20 +9245,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>23</v>
       </c>
       <c t="s" r="K235" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9241,29 +9273,29 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>26</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9278,7 +9310,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9290,10 +9322,10 @@
         <v>101</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9326,7 +9358,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9338,7 +9370,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>55</v>
@@ -9346,7 +9378,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9361,7 +9393,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9373,10 +9405,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9396,7 +9428,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9405,18 +9437,18 @@
         <v>78</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9431,22 +9463,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9464,7 +9496,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9473,13 +9505,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9497,22 +9529,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9545,7 +9577,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9554,18 +9586,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9580,27 +9612,27 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9615,7 +9647,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9624,16 +9656,16 @@
         <v>50</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c t="s" r="K248" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
@@ -9652,29 +9684,29 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="K249" s="7">
         <v>153</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9689,22 +9721,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="K250" s="7">
         <v>97</v>
@@ -9726,22 +9758,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9774,7 +9806,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9794,7 +9826,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9809,7 +9841,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9821,15 +9853,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9844,7 +9876,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9856,15 +9888,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9879,7 +9911,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9891,10 +9923,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9912,7 +9944,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9921,13 +9953,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9945,22 +9977,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9993,7 +10025,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10002,18 +10034,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10028,13 +10060,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>28</v>
@@ -10043,12 +10075,12 @@
         <v>148</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10063,7 +10095,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10075,15 +10107,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10098,7 +10130,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10118,7 +10150,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10133,7 +10165,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10142,18 +10174,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10168,13 +10200,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>28</v>
@@ -10183,7 +10215,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -10216,7 +10248,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10228,15 +10260,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10251,7 +10283,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10260,10 +10292,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>33</v>
@@ -10284,22 +10316,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10332,7 +10364,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -10344,7 +10376,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>133</v>
@@ -10352,7 +10384,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10367,7 +10399,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10387,7 +10419,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10402,7 +10434,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -10411,13 +10443,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10437,19 +10469,19 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>29</v>
@@ -10470,7 +10502,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10479,13 +10511,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10503,19 +10535,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>74</v>
@@ -10551,7 +10583,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10560,18 +10592,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10586,19 +10618,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>19</v>
@@ -10606,7 +10638,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10621,7 +10653,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10636,12 +10668,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10656,7 +10688,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10671,12 +10703,12 @@
         <v>83</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10691,7 +10723,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10700,10 +10732,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>67</v>
@@ -10724,22 +10756,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10772,7 +10804,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10787,7 +10819,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10807,7 +10839,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10822,12 +10854,12 @@
         <v>105</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10842,7 +10874,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10854,15 +10886,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10877,7 +10909,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10886,7 +10918,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>86</v>
@@ -10910,13 +10942,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>28</v>
@@ -10958,7 +10990,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10967,7 +10999,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>52</v>
@@ -10978,7 +11010,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10993,19 +11025,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>83</v>
@@ -11013,7 +11045,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11028,7 +11060,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11037,17 +11069,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>125</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
-      <c r="M293" s="7"/>
+      <c t="s" r="M293" s="7">
+        <v>436</v>
+      </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
       <c t="s" r="A294" s="6">
@@ -11061,22 +11095,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -11109,13 +11143,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>64</v>
@@ -11129,7 +11163,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11144,7 +11178,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11159,11 +11193,13 @@
         <v>23</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
-      <c r="M297" s="7"/>
+      <c t="s" r="M297" s="7">
+        <v>440</v>
+      </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
       <c t="s" r="A298" s="6">
@@ -11177,7 +11213,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11189,7 +11225,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>48</v>
@@ -11225,13 +11261,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>64</v>
@@ -11240,12 +11276,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11260,7 +11296,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11269,18 +11305,18 @@
         <v>64</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>332</v>
+        <v>445</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11295,22 +11331,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11343,7 +11379,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11355,15 +11391,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11378,7 +11414,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11393,12 +11429,12 @@
         <v>133</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11413,7 +11449,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11422,10 +11458,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>69</v>
@@ -11446,19 +11482,19 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>129</v>
@@ -11494,7 +11530,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11514,7 +11550,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11529,7 +11565,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11541,15 +11577,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11564,7 +11600,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11573,7 +11609,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>139</v>
@@ -11584,7 +11620,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11599,13 +11635,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>64</v>
@@ -11647,7 +11683,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11659,7 +11695,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>136</v>
@@ -11682,7 +11718,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11694,15 +11730,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11717,7 +11753,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11737,7 +11773,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11767,7 +11803,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11779,15 +11815,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11802,7 +11838,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11814,15 +11850,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11837,7 +11873,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11857,7 +11893,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11872,7 +11908,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11887,7 +11923,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11905,7 +11941,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11917,7 +11953,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>118</v>
@@ -11953,7 +11989,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11962,18 +11998,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11988,27 +12024,27 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12023,7 +12059,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12035,15 +12071,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12058,7 +12094,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12070,7 +12106,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>22</v>
@@ -12078,7 +12114,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12093,7 +12129,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12102,18 +12138,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I328" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12128,22 +12164,22 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12161,7 +12197,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12170,17 +12206,21 @@
         <v>28</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>193</v>
-      </c>
-      <c r="K330" s="7"/>
+        <v>194</v>
+      </c>
+      <c t="s" r="K330" s="7">
+        <v>227</v>
+      </c>
       <c r="L330" s="7"/>
-      <c r="M330" s="7"/>
+      <c t="s" r="M330" s="7">
+        <v>473</v>
+      </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
       <c t="s" r="A331" s="6">
@@ -12194,22 +12234,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
+        <v>472</v>
+      </c>
+      <c t="s" r="H331" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="I331" s="7">
         <v>464</v>
       </c>
-      <c t="s" r="H331" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="I331" s="7">
-        <v>456</v>
-      </c>
       <c t="s" r="J331" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12242,7 +12282,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12251,18 +12291,18 @@
         <v>64</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12277,13 +12317,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>64</v>
@@ -12297,7 +12337,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12312,7 +12352,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12327,10 +12367,10 @@
         <v>82</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="K335" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
@@ -12349,7 +12389,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12364,14 +12404,14 @@
         <v>44</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="K336" s="7">
         <v>110</v>
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12386,7 +12426,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12398,17 +12438,17 @@
         <v>120</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="K337" s="7">
         <v>25</v>
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12423,7 +12463,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12438,7 +12478,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12471,7 +12511,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12480,10 +12520,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>108</v>
@@ -12491,7 +12531,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12506,27 +12546,27 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12541,7 +12581,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12550,13 +12590,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12574,22 +12614,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12622,7 +12662,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12631,18 +12671,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12657,19 +12697,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>34</v>
@@ -12692,7 +12732,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12701,18 +12741,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12727,27 +12767,27 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12762,7 +12802,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12771,13 +12811,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12795,22 +12835,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12843,7 +12883,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12858,12 +12898,12 @@
         <v>129</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12878,7 +12918,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12890,7 +12930,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>79</v>
@@ -12898,7 +12938,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12913,7 +12953,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12922,10 +12962,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>114</v>
@@ -12933,7 +12973,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12948,27 +12988,27 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12983,7 +13023,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12995,10 +13035,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13016,7 +13056,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13028,10 +13068,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13064,7 +13104,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13076,15 +13116,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13099,7 +13139,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13111,15 +13151,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13134,7 +13174,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13146,15 +13186,15 @@
         <v>78</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13169,7 +13209,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13181,10 +13221,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -13217,7 +13257,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13226,18 +13266,18 @@
         <v>78</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13252,13 +13292,13 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>78</v>
@@ -13272,7 +13312,7 @@
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13287,7 +13327,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13307,7 +13347,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13322,7 +13362,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13334,7 +13374,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>88</v>
@@ -13355,7 +13395,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13367,10 +13407,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13403,7 +13443,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13438,7 +13478,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13453,12 +13493,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13473,7 +13513,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13485,15 +13525,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13508,7 +13548,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13523,12 +13563,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13543,7 +13583,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13552,13 +13592,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13576,13 +13616,13 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>64</v>
@@ -13617,14 +13657,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B377" s="7">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>71</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13636,17 +13676,17 @@
         <v>64</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13661,7 +13701,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13670,7 +13710,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>79</v>
@@ -13683,7 +13723,7 @@
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13698,13 +13738,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>64</v>
@@ -13713,14 +13753,14 @@
         <v>114</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13750,7 +13790,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13765,12 +13805,12 @@
         <v>113</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13785,7 +13825,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13797,10 +13837,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13818,7 +13858,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13827,13 +13867,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13851,22 +13891,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13899,7 +13939,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13911,13 +13951,13 @@
         <v>28</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>107</v>
       </c>
       <c t="s" r="K386" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
@@ -13936,7 +13976,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13948,10 +13988,10 @@
         <v>123</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13971,7 +14011,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13983,14 +14023,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>507</v>
+        <v>363</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
-      <c r="M388" s="7"/>
+      <c t="s" r="M388" s="7">
+        <v>445</v>
+      </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
       <c t="s" r="A389" s="6">
@@ -14004,7 +14046,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14019,7 +14061,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -14037,7 +14079,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14049,10 +14091,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14085,7 +14127,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14094,18 +14136,18 @@
         <v>64</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14120,13 +14162,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>64</v>
@@ -14140,7 +14182,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14155,7 +14197,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14170,7 +14212,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14188,7 +14230,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14200,10 +14242,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14221,7 +14263,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14233,10 +14275,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14269,7 +14311,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14278,18 +14320,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14304,27 +14346,27 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14339,7 +14381,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14351,17 +14393,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>153</v>
       </c>
       <c t="s" r="K400" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14376,7 +14418,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14388,13 +14430,13 @@
         <v>28</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>507</v>
+        <v>363</v>
       </c>
       <c t="s" r="K401" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
@@ -14413,7 +14455,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14425,17 +14467,17 @@
         <v>64</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="K402" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14465,13 +14507,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>120</v>
@@ -14480,14 +14522,14 @@
         <v>129</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="K404" s="7">
         <v>75</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14502,7 +14544,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14511,20 +14553,20 @@
         <v>120</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14539,13 +14581,13 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>120</v>
@@ -14554,14 +14596,14 @@
         <v>91</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14591,7 +14633,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14600,7 +14642,7 @@
         <v>120</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>51</v>
@@ -14611,7 +14653,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14626,13 +14668,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>120</v>
@@ -14641,7 +14683,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14674,7 +14716,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14686,7 +14728,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>25</v>
@@ -14694,7 +14736,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14709,7 +14751,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14718,13 +14760,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14757,7 +14799,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14792,7 +14834,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14807,7 +14849,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14827,7 +14869,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14836,7 +14878,7 @@
         <v>120</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>144</v>
@@ -14875,7 +14917,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14884,13 +14926,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14910,22 +14952,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14958,7 +15000,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14970,15 +15012,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14993,7 +15035,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -15005,7 +15047,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>124</v>
@@ -15016,7 +15058,7 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c t="s" r="A423" s="9">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
@@ -15036,7 +15078,7 @@
     <row r="424" ht="65.25" customHeight="1"/>
     <row r="425" ht="17.25" customHeight="1">
       <c t="s" r="A425" s="10">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B425" s="10"/>
       <c r="C425" s="10"/>
@@ -15049,7 +15091,7 @@
       <c r="J425" s="10"/>
       <c r="K425" s="10"/>
       <c t="s" r="L425" s="11">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="M425" s="11"/>
       <c r="N425" s="11"/>
